--- a/CodeCC/申万一级行业季度收益率矩阵.xlsx
+++ b/CodeCC/申万一级行业季度收益率矩阵.xlsx
@@ -642,7 +642,7 @@
         <v>-22.10527375336362</v>
       </c>
       <c r="T2">
-        <v>10.81163110283019</v>
+        <v>8.721640966841736</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -704,7 +704,7 @@
         <v>-13.01613420969798</v>
       </c>
       <c r="T3">
-        <v>13.65363573758227</v>
+        <v>8.405840671460485</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -766,7 +766,7 @@
         <v>-5.922915206727398</v>
       </c>
       <c r="T4">
-        <v>-4.850046637351769</v>
+        <v>-0.4762482629966036</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -828,7 +828,7 @@
         <v>0.6785203524418915</v>
       </c>
       <c r="T5">
-        <v>-14.77204682104157</v>
+        <v>-12.05818178835378</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -890,7 +890,7 @@
         <v>-19.85717208160533</v>
       </c>
       <c r="T6">
-        <v>-0.4217760042177443</v>
+        <v>1.569388515693904</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -952,7 +952,7 @@
         <v>-20.47869397777849</v>
       </c>
       <c r="T7">
-        <v>1.815124324463091</v>
+        <v>3.282371214746904</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1014,7 +1014,7 @@
         <v>-0.2210877925057031</v>
       </c>
       <c r="T8">
-        <v>-13.57171523196197</v>
+        <v>-10.33955074132558</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1076,7 +1076,7 @@
         <v>-1.095352902498092</v>
       </c>
       <c r="T9">
-        <v>-15.26353280167958</v>
+        <v>-11.81331776576886</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1138,7 +1138,7 @@
         <v>20.60588595841224</v>
       </c>
       <c r="T10">
-        <v>-19.37911535178637</v>
+        <v>-16.45492927691746</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1200,7 +1200,7 @@
         <v>-9.920134883308195</v>
       </c>
       <c r="T11">
-        <v>-8.361976317496577</v>
+        <v>-5.734728851795545</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1262,7 +1262,7 @@
         <v>32.45116199745699</v>
       </c>
       <c r="T12">
-        <v>-26.94399588252324</v>
+        <v>-24.88281275131083</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1324,7 +1324,7 @@
         <v>-14.25520390683828</v>
       </c>
       <c r="T13">
-        <v>3.039397357396068</v>
+        <v>5.545037060908786</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1386,7 +1386,7 @@
         <v>-13.78380267502149</v>
       </c>
       <c r="T14">
-        <v>-9.443375783359787</v>
+        <v>-3.626739304418647</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1448,7 +1448,7 @@
         <v>-6.404131992514939</v>
       </c>
       <c r="T15">
-        <v>2.362718527444274</v>
+        <v>0.2838304703419281</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1510,7 +1510,7 @@
         <v>-4.784220331495947</v>
       </c>
       <c r="T16">
-        <v>-9.667369465459497</v>
+        <v>-4.666253255612052</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1572,7 +1572,7 @@
         <v>-13.58002230642061</v>
       </c>
       <c r="T17">
-        <v>-5.117466233075085</v>
+        <v>-0.7322511635059481</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -1634,7 +1634,7 @@
         <v>-18.48991480861735</v>
       </c>
       <c r="T18">
-        <v>-2.880809888062874</v>
+        <v>3.138995679917556</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -1696,7 +1696,7 @@
         <v>-3.62459658828953</v>
       </c>
       <c r="T19">
-        <v>0.3325421856725574</v>
+        <v>2.777294889942961</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -1758,7 +1758,7 @@
         <v>-18.05911390044893</v>
       </c>
       <c r="T20">
-        <v>5.245182601478504</v>
+        <v>7.138594772083251</v>
       </c>
     </row>
     <row r="21" spans="1:20">
@@ -1820,7 +1820,7 @@
         <v>-11.52085482857177</v>
       </c>
       <c r="T21">
-        <v>-8.00999210806086</v>
+        <v>-1.3155405978307</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -1882,7 +1882,7 @@
         <v>-12.91691672468013</v>
       </c>
       <c r="T22">
-        <v>1.639215925631565</v>
+        <v>3.154236764134155</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -1944,7 +1944,7 @@
         <v>-15.51625631073407</v>
       </c>
       <c r="T23">
-        <v>-10.54204731787304</v>
+        <v>-2.479135294314494</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -2006,7 +2006,7 @@
         <v>-19.51080383679425</v>
       </c>
       <c r="T24">
-        <v>1.86470000713419</v>
+        <v>5.18180304867899</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -2068,7 +2068,7 @@
         <v>85.48070773498375</v>
       </c>
       <c r="T25">
-        <v>-26.42830580497976</v>
+        <v>-28.69840261731759</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -2130,7 +2130,7 @@
         <v>-7.258882320306126</v>
       </c>
       <c r="T26">
-        <v>-6.018540527691929</v>
+        <v>1.356181256347644</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -2192,7 +2192,7 @@
         <v>58.50493006952384</v>
       </c>
       <c r="T27">
-        <v>-18.70329658399422</v>
+        <v>-23.63422193995255</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -2254,7 +2254,7 @@
         <v>-17.1514231687898</v>
       </c>
       <c r="T28">
-        <v>-6.194900765628475</v>
+        <v>6.626031368467999</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -2316,7 +2316,7 @@
         <v>-9.170858002811821</v>
       </c>
       <c r="T29">
-        <v>7.540962299250209</v>
+        <v>7.089571435921171</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -2378,7 +2378,7 @@
         <v>-2.073078113133242</v>
       </c>
       <c r="T30">
-        <v>-0.5435886735887352</v>
+        <v>-1.93166156937894</v>
       </c>
     </row>
     <row r="31" spans="1:20">
@@ -2440,7 +2440,7 @@
         <v>-10.12605556235466</v>
       </c>
       <c r="T31">
-        <v>-4.80775873521988</v>
+        <v>-0.8593064966121999</v>
       </c>
     </row>
     <row r="32" spans="1:20">
@@ -2502,7 +2502,7 @@
         <v>-4.764571509522497</v>
       </c>
       <c r="T32">
-        <v>-14.68461176962038</v>
+        <v>-9.064365655405282</v>
       </c>
     </row>
   </sheetData>
